--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484208_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484208_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0126</v>
+        <v>4.6101</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8153</v>
+        <v>2.8758</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1973</v>
+        <v>1.7343</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4696</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3668</v>
+        <v>0.9643</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2726</v>
+        <v>0.3331</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0942</v>
+        <v>0.6312</v>
       </c>
       <c r="V2" t="n">
         <v>2.748</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5584</v>
+        <v>3.0934</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7834</v>
+        <v>2.0615</v>
       </c>
       <c r="F3" t="n">
-        <v>1.775</v>
+        <v>1.0319</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3608</v>
+        <v>0.8436</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2533</v>
+        <v>-2.3932</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1076</v>
+        <v>3.2369</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1849</v>
+        <v>1.3378</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5375</v>
+        <v>-1.8995</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6475</v>
+        <v>3.2373</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.4941</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2842</v>
+        <v>-0.4937</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5399</v>
+        <v>-0.0004</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0059</v>
+        <v>0.4684</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5752</v>
+        <v>0.4465</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4308</v>
+        <v>0.0219</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9962</v>
+        <v>0.6093</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9962</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5541</v>
+        <v>2.8627</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5766</v>
+        <v>1.1966</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9775</v>
+        <v>1.666</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8436</v>
+        <v>1.3608</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.3932</v>
+        <v>1.2533</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2369</v>
+        <v>0.1076</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3378</v>
+        <v>2.1849</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.8995</v>
+        <v>1.5375</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2373</v>
+        <v>0.6475</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4941</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4937</v>
+        <v>-0.2842</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0004</v>
+        <v>-0.5399</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
         <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.3102</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0384</v>
+        <v>-0.0116</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0326</v>
+        <v>0.3218</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6093</v>
+        <v>0.9962</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3321</v>
+        <v>0.9962</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.791</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3456</v>
+        <v>0.5072</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5017</v>
+        <v>0.2838</v>
       </c>
       <c r="G5" t="n">
         <v>0.3597</v>
@@ -844,13 +844,13 @@
         <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0985</v>
+        <v>-0.1548</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2888</v>
+        <v>-0.1272</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1903</v>
+        <v>-0.0275</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0822</v>
+        <v>0.615</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5804</v>
+        <v>1.086</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4983</v>
+        <v>-0.471</v>
       </c>
       <c r="G6" t="n">
         <v>1.3845</v>
@@ -922,13 +922,13 @@
         <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6697</v>
+        <v>-0.1369</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5447</v>
+        <v>-0.0391</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.125</v>
+        <v>-0.0978</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2186</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9772</v>
+        <v>0.408</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3393</v>
+        <v>1.3704</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3165</v>
+        <v>-0.9624</v>
       </c>
       <c r="G7" t="n">
         <v>0.6363</v>
@@ -1000,13 +1000,13 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7269</v>
+        <v>0.6582</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4842</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2427</v>
+        <v>0.1113</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8865</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4681</v>
+        <v>0.0306</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8805</v>
+        <v>2.355</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4125</v>
+        <v>-2.3243</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.8733</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.4969</v>
+        <v>0.3901</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3764</v>
+        <v>-0.2969</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.8156</v>
+        <v>1.9416</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.0584</v>
+        <v>0.6191</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2428</v>
+        <v>1.3225</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0577</v>
+        <v>-1.8484</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4384</v>
+        <v>-0.2289</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6192</v>
+        <v>-1.6194</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>4.247</v>
+        <v>0.2277</v>
       </c>
       <c r="T8" t="n">
-        <v>3.401</v>
+        <v>0.1715</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8461</v>
+        <v>0.0562</v>
       </c>
       <c r="V8" t="n">
-        <v>1.307</v>
+        <v>-1.4624</v>
       </c>
       <c r="W8" t="n">
-        <v>1.441</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.134</v>
+        <v>-2.681</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7262</v>
+        <v>-2.969</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0611</v>
+        <v>-1.0086</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7873</v>
+        <v>-1.9604</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09320000000000001</v>
+        <v>-1.5668</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3901</v>
+        <v>-0.5285</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2969</v>
+        <v>-1.0383</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9416</v>
+        <v>-0.6132</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6191</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3225</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8484</v>
+        <v>-0.9536</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2289</v>
+        <v>-0.549</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6194</v>
+        <v>-0.4047</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5291</v>
+        <v>0.1252</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1224</v>
+        <v>0.3041</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4068</v>
+        <v>-0.1789</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4624</v>
+        <v>-0.9414</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.681</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8213</v>
+        <v>-4.0539</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8063</v>
+        <v>-4.0851</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0149</v>
+        <v>0.0312</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5668</v>
+        <v>-4.8733</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5285</v>
+        <v>-3.4969</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0383</v>
+        <v>-1.3764</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6132</v>
+        <v>-2.8156</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0205</v>
+        <v>-3.0584</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.2428</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9536</v>
+        <v>-2.0577</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.549</v>
+        <v>-0.4384</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4047</v>
+        <v>-1.6192</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.586</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>0.273</v>
+        <v>1.6611</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5063</v>
+        <v>1.1964</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2333</v>
+        <v>0.4648</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9414</v>
+        <v>1.307</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>1.441</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>-0.134</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.306</v>
+        <v>-4.7122</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0323</v>
+        <v>-2.5474</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2738</v>
+        <v>-2.1648</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2425</v>
@@ -1312,13 +1312,13 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5464</v>
+        <v>0.0475</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.3019</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2404</v>
+        <v>0.3494</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1265</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.220000000000001</v>
+        <v>-7.9295</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.9844</v>
+        <v>-6.8028</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2356</v>
+        <v>-1.1267</v>
       </c>
       <c r="G12" t="n">
         <v>-6.6629</v>
@@ -1390,13 +1390,13 @@
         <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1144</v>
+        <v>0.1761</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2863</v>
+        <v>0.4679</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4007</v>
+        <v>-0.2918</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4661</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.4642</v>
+        <v>-7.253800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2018</v>
+        <v>-2.991399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.262400000000001</v>
+        <v>-4.2624</v>
       </c>
       <c r="G13" t="n">
         <v>-11.137</v>
@@ -1438,7 +1438,7 @@
         <v>-5.742000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.3947</v>
+        <v>-5.394699999999999</v>
       </c>
       <c r="J13" t="n">
         <v>0.2010000000000005</v>
@@ -1447,7 +1447,7 @@
         <v>-3.8502</v>
       </c>
       <c r="L13" t="n">
-        <v>4.051599999999999</v>
+        <v>4.0516</v>
       </c>
       <c r="M13" t="n">
         <v>-11.338</v>
@@ -1456,7 +1456,7 @@
         <v>-1.8915</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.446299999999999</v>
+        <v>-9.446300000000001</v>
       </c>
       <c r="P13" t="n">
         <v>0.9766999999999996</v>
@@ -1468,13 +1468,13 @@
         <v>12.6973</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1367</v>
+        <v>4.347</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7761</v>
+        <v>2.9866</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3607</v>
+        <v>1.3606</v>
       </c>
       <c r="V13" t="n">
         <v>-1.440999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7631</v>
+        <v>6.3776</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7383</v>
+        <v>7.2439</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9752</v>
+        <v>-0.8663</v>
       </c>
       <c r="G14" t="n">
         <v>7.904</v>
@@ -1546,13 +1546,13 @@
         <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9922</v>
+        <v>-0.3776</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7125</v>
+        <v>-0.2069</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2797</v>
+        <v>-0.1707</v>
       </c>
       <c r="V14" t="n">
         <v>0.6093</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3058</v>
+        <v>4.8843</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1355</v>
+        <v>1.9333</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1702</v>
+        <v>2.951</v>
       </c>
       <c r="G15" t="n">
         <v>3.8473</v>
@@ -1624,13 +1624,13 @@
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2398</v>
+        <v>-0.1817</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1732</v>
+        <v>-0.3754</v>
       </c>
       <c r="U15" t="n">
-        <v>0.413</v>
+        <v>0.1938</v>
       </c>
       <c r="V15" t="n">
         <v>1.2186</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8654</v>
+        <v>4.2011</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8676</v>
+        <v>1.0699</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9978</v>
+        <v>3.1313</v>
       </c>
       <c r="G16" t="n">
         <v>3.3087</v>
@@ -1702,13 +1702,13 @@
         <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4898</v>
+        <v>-0.1541</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5777</v>
+        <v>-0.3754</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.2213</v>
       </c>
       <c r="V16" t="n">
         <v>1.8279</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7699</v>
+        <v>2.4882</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4729</v>
+        <v>1.6751</v>
       </c>
       <c r="F17" t="n">
-        <v>0.297</v>
+        <v>0.8131</v>
       </c>
       <c r="G17" t="n">
         <v>3.3747</v>
@@ -1780,13 +1780,13 @@
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.281</v>
+        <v>-0.5627</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.7056</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3732</v>
+        <v>0.143</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4959</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1115</v>
+        <v>1.3868</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2576</v>
+        <v>3.5323</v>
       </c>
       <c r="F18" t="n">
-        <v>1.369</v>
+        <v>-2.1454</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5748</v>
+        <v>0.4956</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06370000000000001</v>
+        <v>1.1965</v>
       </c>
       <c r="I18" t="n">
-        <v>1.511</v>
+        <v>-0.7009</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7108</v>
+        <v>1.7344</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5308</v>
+        <v>1.086</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2416</v>
+        <v>0.6484</v>
       </c>
       <c r="M18" t="n">
-        <v>0.864</v>
+        <v>-1.2388</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5946</v>
+        <v>0.1105</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2694</v>
+        <v>-1.3494</v>
       </c>
       <c r="P18" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.1953</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.9767</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.268</v>
+        <v>-0.6128</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0083</v>
+        <v>-0.112</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2763</v>
+        <v>-0.5009</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0317</v>
+        <v>1.2404</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4452</v>
+        <v>0.5463</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5865</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0669</v>
@@ -1936,13 +1936,13 @@
         <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5107</v>
+        <v>-0.302</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2421</v>
+        <v>-0.141</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2686</v>
+        <v>-0.161</v>
       </c>
       <c r="V19" t="n">
         <v>1.2186</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4353</v>
+        <v>1.1063</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8245</v>
+        <v>-0.5609</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3892</v>
+        <v>1.6673</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4956</v>
+        <v>1.5748</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1965</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7009</v>
+        <v>1.511</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7344</v>
+        <v>0.7108</v>
       </c>
       <c r="K20" t="n">
-        <v>1.086</v>
+        <v>-0.5308</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6484</v>
+        <v>1.2416</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2388</v>
+        <v>0.864</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1105</v>
+        <v>0.5946</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3494</v>
+        <v>0.2694</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5644</v>
+        <v>-0.2731</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8198</v>
+        <v>-0.295</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7446</v>
+        <v>0.0219</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6972</v>
+        <v>-2.2858</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3569</v>
+        <v>-2.8624</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6597</v>
+        <v>0.5766</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0908</v>
@@ -2248,13 +2248,13 @@
         <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.2153</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5284</v>
+        <v>0.0229</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2755</v>
+        <v>0.1924</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9962</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4546</v>
+        <v>-3.3193</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4459</v>
+        <v>-2.2548</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0087</v>
+        <v>-1.0645</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8687</v>
@@ -2326,13 +2326,13 @@
         <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2541</v>
+        <v>0.3893</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1558</v>
+        <v>0.3469</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0983</v>
+        <v>0.0425</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2772</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6041</v>
+        <v>-6.2048</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.0987</v>
+        <v>-5.9976</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.2072</v>
       </c>
       <c r="G25" t="n">
         <v>-5.3418</v>
@@ -2404,13 +2404,13 @@
         <v>1.1721</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5981</v>
+        <v>-0.1988</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1102</v>
+        <v>0.2113</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7083</v>
+        <v>-0.4101</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6642</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.464300000000005</v>
+        <v>9.812300000000008</v>
       </c>
       <c r="E26" t="n">
-        <v>4.2624</v>
+        <v>4.262600000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>4.2016</v>
+        <v>5.55</v>
       </c>
       <c r="G26" t="n">
         <v>11.1369</v>
@@ -2482,13 +2482,13 @@
         <v>11.7207</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.1368</v>
+        <v>-1.7886</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.3608</v>
+        <v>-1.3606</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.776</v>
+        <v>-0.4278000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>1.4409</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484208_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484208_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2437</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0.9962</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +819,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.791</v>
+        <v>0.914</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5072</v>
+        <v>0.914</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2838</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3597</v>
+        <v>0.914</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3599</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0002</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6344</v>
+        <v>0.914</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6344</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2747</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2745</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1548</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1272</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0275</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -860,12 +880,17 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +902,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.615</v>
+        <v>0.791</v>
       </c>
       <c r="E6" t="n">
-        <v>1.086</v>
+        <v>0.5072</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.471</v>
+        <v>0.2838</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3845</v>
+        <v>0.3597</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7491</v>
+        <v>0.3599</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3646</v>
+        <v>-0.0002</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1251</v>
+        <v>0.6344</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0847</v>
+        <v>0.6344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2593</v>
+        <v>-0.2747</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6644</v>
+        <v>-0.2745</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4051</v>
+        <v>-0.0002</v>
       </c>
       <c r="P6" t="n">
         <v>0.586</v>
@@ -922,28 +947,33 @@
         <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1369</v>
+        <v>-0.1548</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0391</v>
+        <v>-0.1272</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0978</v>
+        <v>-0.0275</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.408</v>
+        <v>0.615</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3704</v>
+        <v>1.086</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9624</v>
+        <v>-0.471</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6363</v>
+        <v>1.3845</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.07829999999999999</v>
+        <v>1.7491</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7146</v>
+        <v>-0.3646</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8002</v>
+        <v>1.1251</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2635</v>
+        <v>1.0847</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0638</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1639</v>
+        <v>0.2593</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1852</v>
+        <v>0.6644</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3492</v>
+        <v>-0.4051</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6582</v>
+        <v>-0.1369</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5469000000000001</v>
+        <v>-0.0391</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1113</v>
+        <v>-0.0978</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0306</v>
+        <v>0.408</v>
       </c>
       <c r="E8" t="n">
-        <v>2.355</v>
+        <v>1.3704</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3243</v>
+        <v>-0.9624</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.6363</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3901</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2969</v>
+        <v>0.7146</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9416</v>
+        <v>1.8002</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6191</v>
+        <v>-0.2635</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3225</v>
+        <v>2.0638</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8484</v>
+        <v>-1.1639</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2289</v>
+        <v>0.1852</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6194</v>
+        <v>-1.3492</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2277</v>
+        <v>0.6582</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1715</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0562</v>
+        <v>0.1113</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4624</v>
+        <v>-0.8865</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.681</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.969</v>
+        <v>-0.8833</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0086</v>
+        <v>1.441</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9604</v>
+        <v>-2.3243</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5668</v>
+        <v>-0.8207</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5285</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0383</v>
+        <v>-0.9039</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6132</v>
+        <v>1.0276</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0205</v>
+        <v>0.3121</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.7156</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9536</v>
+        <v>-1.8484</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.549</v>
+        <v>-0.2289</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4047</v>
+        <v>-1.6194</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1252</v>
+        <v>0.2277</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3041</v>
+        <v>0.1715</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1789</v>
+        <v>0.0562</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9414</v>
+        <v>-1.4624</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-2.681</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0539</v>
+        <v>-2.969</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0851</v>
+        <v>-1.0086</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0312</v>
+        <v>-1.9604</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.8733</v>
+        <v>-1.5668</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.4969</v>
+        <v>-0.5285</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3764</v>
+        <v>-1.0383</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8156</v>
+        <v>-0.6132</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.0584</v>
+        <v>0.0205</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2428</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0577</v>
+        <v>-0.9536</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4384</v>
+        <v>-0.549</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6192</v>
+        <v>-0.4047</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1488</v>
+        <v>-0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6611</v>
+        <v>0.1252</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1964</v>
+        <v>0.3041</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4648</v>
+        <v>-0.1789</v>
       </c>
       <c r="V10" t="n">
-        <v>1.307</v>
+        <v>-0.9414</v>
       </c>
       <c r="W10" t="n">
-        <v>1.441</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.134</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7122</v>
+        <v>-4.0539</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5474</v>
+        <v>-4.0851</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1648</v>
+        <v>0.0312</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2425</v>
+        <v>-4.8733</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3796</v>
+        <v>-3.4969</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8628</v>
+        <v>-1.3764</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6046</v>
+        <v>-2.8156</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5513</v>
+        <v>-3.0584</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0533</v>
+        <v>0.2428</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6379</v>
+        <v>-2.0577</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8283</v>
+        <v>-0.4384</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8095</v>
+        <v>-1.6192</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0475</v>
+        <v>1.6611</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3019</v>
+        <v>1.1964</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3494</v>
+        <v>0.4648</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1265</v>
+        <v>1.307</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>1.441</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4624</v>
+        <v>-0.134</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q. ROIG GARCIA</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.9295</v>
+        <v>-4.7122</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8028</v>
+        <v>-2.5474</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1267</v>
+        <v>-2.1648</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.6629</v>
+        <v>-2.2425</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3751</v>
+        <v>-1.3796</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.2878</v>
+        <v>-0.8628</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.3406</v>
+        <v>-0.6046</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.6718</v>
+        <v>-0.5513</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.6688</v>
+        <v>-0.0533</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3223</v>
+        <v>-1.6379</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7032</v>
+        <v>-0.8283</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.619</v>
+        <v>-0.8095</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1761</v>
+        <v>0.0475</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4679</v>
+        <v>-0.3019</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2918</v>
+        <v>0.3494</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4661</v>
+        <v>-2.1265</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4661</v>
+        <v>-1.4624</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>Q. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.253800000000001</v>
+        <v>-7.9295</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.991399999999999</v>
+        <v>-6.8028</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2624</v>
+        <v>-1.1267</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.137</v>
+        <v>-6.6629</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.742000000000001</v>
+        <v>-2.3751</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.394699999999999</v>
+        <v>-4.2878</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2010000000000005</v>
+        <v>-4.3406</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.8502</v>
+        <v>-1.6718</v>
       </c>
       <c r="L13" t="n">
-        <v>4.0516</v>
+        <v>-2.6688</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.338</v>
+        <v>-2.3223</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8915</v>
+        <v>-0.7032</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.446300000000001</v>
+        <v>-1.619</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9766999999999996</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.7205</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>12.6973</v>
+        <v>1.9534</v>
       </c>
       <c r="S13" t="n">
-        <v>4.347</v>
+        <v>0.1761</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9866</v>
+        <v>0.4679</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3606</v>
+        <v>-0.2918</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.440999999999999</v>
+        <v>-0.4661</v>
       </c>
       <c r="W13" t="n">
-        <v>5.541499999999999</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.9826</v>
+        <v>-0.4661</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DM GROUP MOLLET</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3776</v>
+        <v>-7.253699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2439</v>
+        <v>-2.991399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8663</v>
+        <v>-4.2624</v>
       </c>
       <c r="G14" t="n">
-        <v>7.904</v>
+        <v>-11.1369</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2502</v>
+        <v>-5.742000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6538</v>
+        <v>-5.3947</v>
       </c>
       <c r="J14" t="n">
-        <v>9.4125</v>
+        <v>0.2009999999999987</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2745</v>
+        <v>-3.8502</v>
       </c>
       <c r="L14" t="n">
-        <v>6.138</v>
+        <v>4.051699999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5085</v>
+        <v>-11.338</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0243</v>
+        <v>-1.8915</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4842</v>
+        <v>-9.446300000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.7581</v>
+        <v>0.9766999999999996</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1255</v>
+        <v>-11.7205</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>12.6973</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3776</v>
+        <v>4.347</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2069</v>
+        <v>2.9866</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1707</v>
+        <v>1.3606</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6093</v>
+        <v>-1.441</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1638</v>
+        <v>5.541499999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5545</v>
-      </c>
+        <v>-6.9826</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8843</v>
+        <v>6.3776</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9333</v>
+        <v>7.2439</v>
       </c>
       <c r="F15" t="n">
-        <v>2.951</v>
+        <v>-0.8663</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8473</v>
+        <v>7.904</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0384</v>
+        <v>3.2502</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8089</v>
+        <v>4.6538</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0631</v>
+        <v>9.4125</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2538</v>
+        <v>3.2745</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8093</v>
+        <v>6.138</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7843</v>
+        <v>-1.5085</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7846</v>
+        <v>-0.0243</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0004</v>
+        <v>-1.4842</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1817</v>
+        <v>-0.3776</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3754</v>
+        <v>-0.2069</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1938</v>
+        <v>-0.1707</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2224</v>
+        <v>1.1638</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9962</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2011</v>
+        <v>4.8843</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0699</v>
+        <v>1.9333</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1313</v>
+        <v>2.951</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3087</v>
+        <v>3.8473</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6247</v>
+        <v>3.0384</v>
       </c>
       <c r="I16" t="n">
-        <v>2.684</v>
+        <v>0.8089</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5708</v>
+        <v>3.0631</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3044</v>
+        <v>2.2538</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8752</v>
+        <v>0.8093</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7379</v>
+        <v>0.7843</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9292</v>
+        <v>0.7846</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8087</v>
+        <v>-0.0004</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1541</v>
+        <v>-0.1817</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3754</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2213</v>
+        <v>0.1938</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8279</v>
+        <v>1.2186</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8279</v>
+        <v>0.2224</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.9962</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4882</v>
+        <v>4.2011</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6751</v>
+        <v>1.0699</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8131</v>
+        <v>3.1313</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3747</v>
+        <v>3.3087</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7675</v>
+        <v>0.6247</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6072</v>
+        <v>2.684</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3807</v>
+        <v>1.5708</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3126</v>
+        <v>-0.3044</v>
       </c>
       <c r="L17" t="n">
-        <v>0.06809999999999999</v>
+        <v>1.8752</v>
       </c>
       <c r="M17" t="n">
-        <v>0.994</v>
+        <v>1.7379</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4549</v>
+        <v>0.9292</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5391</v>
+        <v>0.8087</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5627</v>
+        <v>-0.1541</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7056</v>
+        <v>-0.3754</v>
       </c>
       <c r="U17" t="n">
-        <v>0.143</v>
+        <v>0.2213</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4959</v>
+        <v>1.8279</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3868</v>
+        <v>2.4882</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5323</v>
+        <v>1.6751</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1454</v>
+        <v>0.8131</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4956</v>
+        <v>3.3747</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1965</v>
+        <v>2.7675</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7009</v>
+        <v>0.6072</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7344</v>
+        <v>2.3807</v>
       </c>
       <c r="K18" t="n">
-        <v>1.086</v>
+        <v>2.3126</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6484</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2388</v>
+        <v>0.994</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1105</v>
+        <v>0.4549</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3494</v>
+        <v>0.5391</v>
       </c>
       <c r="P18" t="n">
         <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6128</v>
+        <v>-0.5627</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.112</v>
+        <v>-0.7056</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5009</v>
+        <v>0.143</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7731</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2404</v>
+        <v>1.3868</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5463</v>
+        <v>3.5323</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6941000000000001</v>
+        <v>-2.1454</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0669</v>
+        <v>0.4956</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1072</v>
+        <v>1.1965</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0403</v>
+        <v>-0.7009</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5313</v>
+        <v>1.7344</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5718</v>
+        <v>1.086</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>0.6484</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4644</v>
+        <v>-1.2388</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4646</v>
+        <v>0.1105</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0002</v>
+        <v>-1.3494</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.302</v>
+        <v>-0.6128</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.141</v>
+        <v>-0.112</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.161</v>
+        <v>-0.5009</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2186</v>
+        <v>0.3321</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>2.1052</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1063</v>
+        <v>1.2404</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5609</v>
+        <v>0.5463</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6673</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5748</v>
+        <v>-0.0669</v>
       </c>
       <c r="H20" t="n">
-        <v>0.06370000000000001</v>
+        <v>-0.1072</v>
       </c>
       <c r="I20" t="n">
-        <v>1.511</v>
+        <v>0.0403</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7108</v>
+        <v>-0.5313</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5308</v>
+        <v>-0.5718</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2416</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>0.864</v>
+        <v>0.4644</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5946</v>
+        <v>0.4646</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2694</v>
+        <v>-0.0002</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2731</v>
+        <v>-0.302</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.295</v>
+        <v>-0.141</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0219</v>
+        <v>-0.161</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1348</v>
+        <v>1.1063</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1348</v>
+        <v>-0.5609</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.6673</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1.5748</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1.511</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7108</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.5308</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.2416</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.864</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.5946</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.2694</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1348</v>
+        <v>-0.2731</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1348</v>
+        <v>-0.295</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.0219</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2108,12 +2204,17 @@
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SPAHNI MORADO</t>
+          <t>J. SERRA SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,10 +2226,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1973</v>
+        <v>0.1348</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1973</v>
+        <v>0.1348</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2179,19 +2280,24 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>M. SPAHNI MORADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2858</v>
+        <v>-0.1973</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8624</v>
+        <v>-0.1973</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5766</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0908</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3103</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7805</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9356</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8302</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1054</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1552</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5199</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6751</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2153</v>
+        <v>0.1348</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0229</v>
+        <v>0.1348</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1924</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9962</v>
+        <v>-0.3321</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2224</v>
+        <v>-0.3321</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3193</v>
+        <v>-2.2858</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2548</v>
+        <v>-2.8624</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0645</v>
+        <v>0.5766</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8687</v>
+        <v>-2.0908</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1665</v>
+        <v>-0.3103</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-1.7805</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6948</v>
+        <v>-1.9356</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9376</v>
+        <v>-0.8302</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2428</v>
+        <v>-1.1054</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1739</v>
+        <v>-0.1552</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2289</v>
+        <v>0.5199</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9449</v>
+        <v>-0.6751</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3893</v>
+        <v>0.2153</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3469</v>
+        <v>0.0229</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0425</v>
+        <v>0.1924</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2772</v>
+        <v>-0.9962</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2186</v>
+        <v>0.2224</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2048</v>
+        <v>-3.3193</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9976</v>
+        <v>-2.2548</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2072</v>
+        <v>-1.0645</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.3418</v>
+        <v>-1.8687</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.615</v>
+        <v>-1.1665</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7268</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.3726</v>
+        <v>-0.6948</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.8604</v>
+        <v>-0.9376</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5122</v>
+        <v>0.2428</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9692</v>
+        <v>-1.1739</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2454</v>
+        <v>-0.2289</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2146</v>
+        <v>-0.9449</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1721</v>
+        <v>-3.1255</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1988</v>
+        <v>0.3893</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2113</v>
+        <v>0.3469</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4101</v>
+        <v>0.0425</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6642</v>
+        <v>-0.2772</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,152 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-6.2048</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-5.9976</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.2072</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-5.3418</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.615</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.7268</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-4.3726</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-3.8604</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.5122</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.9692</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.2146</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.1988</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.2113</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.4101</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484208_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>9.812300000000008</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>4.262600000000001</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>5.55</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G27" t="n">
         <v>11.1369</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H27" t="n">
         <v>5.742000000000003</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>5.394900000000001</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>11.338</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K27" t="n">
         <v>1.891700000000001</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>9.446300000000003</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>-0.2010000000000002</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>3.850500000000001</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O27" t="n">
         <v>-4.051600000000001</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P27" t="n">
         <v>-0.9766</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q27" t="n">
         <v>-12.6973</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>11.7207</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>-1.7886</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>-1.3606</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>-0.4278000000000001</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V27" t="n">
         <v>1.4409</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W27" t="n">
         <v>6.982600000000001</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X27" t="n">
         <v>-5.541799999999999</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
